--- a/excel_files/mappings.xlsx
+++ b/excel_files/mappings.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\src\generated_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23ED773D-5C5A-4E85-977F-F049BD26EC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98BC229D-7433-4E48-BAE4-952CC2A1708E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8232" yWindow="-13068" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15" yWindow="16170" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sources" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="262">
   <si>
     <t>Windows Display</t>
   </si>
@@ -720,12 +721,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Commewnts</t>
-  </si>
-  <si>
-    <t>PITA!!! Tag editors inconsistent handling this metadata</t>
-  </si>
-  <si>
     <t>needs manual updates once mp3 converted</t>
   </si>
   <si>
@@ -769,6 +764,81 @@
   </si>
   <si>
     <t>https://docs.mp3tag.de/mapping-table/</t>
+  </si>
+  <si>
+    <t>VORBIS (flac)</t>
+  </si>
+  <si>
+    <t>https://web.archive.org/web/20040401200215/reactor-core.org/ogg-tag-recommendations.html</t>
+  </si>
+  <si>
+    <t>TRACKNUMBER</t>
+  </si>
+  <si>
+    <t>ALBUMARTIST</t>
+  </si>
+  <si>
+    <t>COMPOSER</t>
+  </si>
+  <si>
+    <t>COPYRIGHT</t>
+  </si>
+  <si>
+    <t>GENRE</t>
+  </si>
+  <si>
+    <t>PUBLISHER</t>
+  </si>
+  <si>
+    <t>TITLE</t>
+  </si>
+  <si>
+    <t>ALBUM</t>
+  </si>
+  <si>
+    <t>ARTIST</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>COMMENT</t>
+  </si>
+  <si>
+    <t>ORGANIZATION is also possible</t>
+  </si>
+  <si>
+    <t>METADATA_BLOCK_PICTURE</t>
+  </si>
+  <si>
+    <t>according to Google</t>
+  </si>
+  <si>
+    <t>ID3v2.3 Comments</t>
+  </si>
+  <si>
+    <t>Vorbis Comments</t>
+  </si>
+  <si>
+    <t>must be in ISO 8601 format</t>
+  </si>
+  <si>
+    <t>Vorbis data type</t>
+  </si>
+  <si>
+    <t>singleton UTF-8</t>
+  </si>
+  <si>
+    <t>prob singleton UTF-8</t>
+  </si>
+  <si>
+    <t>multiple UTF-8</t>
+  </si>
+  <si>
+    <t>DISCNUMBER</t>
+  </si>
+  <si>
+    <t>Tag editors inconsistent handling this metadata</t>
   </si>
 </sst>
 </file>
@@ -924,7 +994,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1001,6 +1071,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1261,28 +1340,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="50.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="68.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="45.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="67.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" customHeight="1">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>191</v>
@@ -1300,19 +1382,28 @@
         <v>113</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="K1" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="18.75" customHeight="1">
+    <row r="2" spans="1:14" ht="15.75">
       <c r="A2" s="23" t="s">
         <v>69</v>
       </c>
@@ -1334,16 +1425,27 @@
       <c r="G2" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="H2" s="25"/>
+      <c r="I2" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="J2" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-    </row>
-    <row r="3" spans="1:11" ht="18.75" customHeight="1">
+      <c r="K2" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="L2" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="M2" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="N2" s="28" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="15.75">
       <c r="A3" s="23" t="s">
         <v>4</v>
       </c>
@@ -1365,18 +1467,25 @@
       <c r="G3" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="24"/>
+      <c r="I3" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="24" t="s">
+      <c r="J3" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="15"/>
-      <c r="K3" s="28" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="18.75" customHeight="1">
+      <c r="K3" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="L3" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="M3" s="24"/>
+      <c r="N3" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15.75">
       <c r="A4" s="23" t="s">
         <v>10</v>
       </c>
@@ -1398,519 +1507,611 @@
       <c r="G4" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="24"/>
+      <c r="I4" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="J4" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="K4" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="L4" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="N4" s="29" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15.75">
+      <c r="A5" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="L5" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15.75">
+      <c r="A6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="L6" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="15"/>
+    </row>
+    <row r="7" spans="1:14" ht="15.75">
+      <c r="A7" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="L7" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="M7" s="24"/>
+      <c r="N7" s="15"/>
+    </row>
+    <row r="8" spans="1:14" ht="15.75">
+      <c r="A8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="L8" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="M8" s="7"/>
+      <c r="N8" s="15"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.75">
+      <c r="A9" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="L9" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="M9" s="24"/>
+      <c r="N9" s="15"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="I10" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="J10" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="K10" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="L10" s="26"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="15"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="15"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="15"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="15"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="K14" s="11"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="15"/>
+    </row>
+    <row r="15" spans="1:14" ht="15.75">
+      <c r="A15" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="L15" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="M15" s="24"/>
+      <c r="N15" s="15"/>
+    </row>
+    <row r="16" spans="1:14" ht="15.75">
+      <c r="A16" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="L16" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="N16" s="15"/>
+    </row>
+    <row r="17" spans="1:14" ht="15.75">
+      <c r="A17" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="J17" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="L17" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="M17" s="24"/>
+      <c r="N17" s="15"/>
+    </row>
+    <row r="18" spans="1:14" ht="15.75">
+      <c r="A18" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="L18" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="M18" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="1:14" ht="15.75">
+      <c r="A19" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="C19" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="J5" s="15"/>
-      <c r="K5" s="29" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A6" s="15" t="s">
+      <c r="F19" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="15"/>
+    </row>
+    <row r="20" spans="1:14" ht="15.75">
+      <c r="A20" s="15" t="s">
         <v>170</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="J6" s="15"/>
-      <c r="K6" s="19" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A7" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A8" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A9" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A11" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A13" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="H13" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-    </row>
-    <row r="14" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A14" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-    </row>
-    <row r="15" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-    </row>
-    <row r="16" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-    </row>
-    <row r="17" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A17" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-    </row>
-    <row r="18" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A18" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="I18" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-    </row>
-    <row r="19" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="K19" s="15"/>
-    </row>
-    <row r="20" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A20" s="4" t="s">
-        <v>165</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>218</v>
+        <v>160</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>160</v>
@@ -1918,49 +2119,55 @@
       <c r="G20" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>160</v>
-      </c>
+      <c r="H20" s="3"/>
       <c r="I20" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-    </row>
-    <row r="21" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A21" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="H21" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="I21" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-    </row>
-    <row r="22" spans="1:11" ht="18.75" customHeight="1">
+      <c r="J20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="15"/>
+    </row>
+    <row r="21" spans="1:14" ht="15.75">
+      <c r="A21" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="15"/>
+    </row>
+    <row r="22" spans="1:14" ht="15.75">
       <c r="A22" s="5" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>35</v>
@@ -1972,152 +2179,169 @@
         <v>160</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>235</v>
+        <v>119</v>
       </c>
       <c r="G22" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="15"/>
+    </row>
+    <row r="23" spans="1:14" ht="15.75">
+      <c r="A23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H22" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-    </row>
-    <row r="23" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A23" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="E23" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="F23" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="G23" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="H23" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="I23" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="J23" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="K23" s="15"/>
-    </row>
-    <row r="24" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A24" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B24" s="5" t="s">
+      <c r="H23" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="15"/>
+    </row>
+    <row r="24" spans="1:14" ht="15.75">
+      <c r="A24" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-    </row>
-    <row r="25" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="C24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="15"/>
+    </row>
+    <row r="25" spans="1:14" ht="15.75">
+      <c r="A25" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="I25" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-    </row>
-    <row r="26" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A26" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="H26" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="I26" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-    </row>
-    <row r="27" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A27" s="14" t="s">
-        <v>167</v>
+      <c r="C25" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H25" s="5"/>
+      <c r="I25" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="15"/>
+    </row>
+    <row r="26" spans="1:14" ht="15.75">
+      <c r="A26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="15"/>
+    </row>
+    <row r="27" spans="1:14" ht="15.75">
+      <c r="A27" s="5" t="s">
+        <v>184</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>35</v>
@@ -2129,7 +2353,7 @@
         <v>160</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>160</v>
@@ -2137,92 +2361,103 @@
       <c r="G27" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="H27" s="5" t="s">
-        <v>135</v>
-      </c>
+      <c r="H27" s="5"/>
       <c r="I27" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-    </row>
-    <row r="28" spans="1:11" ht="18.75" customHeight="1">
+        <v>160</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="15"/>
+    </row>
+    <row r="28" spans="1:14" ht="15.75">
       <c r="A28" s="6" t="s">
-        <v>166</v>
+        <v>46</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>47</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>160</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="H28" s="5"/>
       <c r="I28" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-    </row>
-    <row r="29" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A29" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="B29" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="15"/>
+    </row>
+    <row r="29" spans="1:14" ht="15.75">
+      <c r="A29" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-    </row>
-    <row r="30" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A30" s="15" t="s">
-        <v>169</v>
+      <c r="C29" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="I29" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="15"/>
+    </row>
+    <row r="30" spans="1:14" ht="15.75">
+      <c r="A30" s="4" t="s">
+        <v>165</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>160</v>
+        <v>204</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>160</v>
@@ -2230,212 +2465,225 @@
       <c r="G30" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="I30" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="J30" s="15"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A31" s="6" t="s">
-        <v>225</v>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="15"/>
+    </row>
+    <row r="31" spans="1:14" ht="15.75">
+      <c r="A31" s="5" t="s">
+        <v>183</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="15"/>
+    </row>
+    <row r="32" spans="1:14" ht="15.75">
+      <c r="A32" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="15"/>
+    </row>
+    <row r="33" spans="1:14" ht="15.75">
+      <c r="A33" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H33" s="3"/>
+      <c r="I33" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J33" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="15"/>
+    </row>
+    <row r="34" spans="1:14" ht="15.75">
+      <c r="A34" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="15"/>
+    </row>
+    <row r="35" spans="1:14" ht="15.75">
+      <c r="A35" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J35" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="36" spans="1:14" ht="15.75">
+      <c r="A36" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F31" s="5" t="s">
+      <c r="E36" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G36" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="H31" s="21" t="s">
+      <c r="H36" s="5"/>
+      <c r="I36" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="I31" s="21" t="s">
+      <c r="J36" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-    </row>
-    <row r="32" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A32" s="3" t="s">
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="15"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-    </row>
-    <row r="33" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A33" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="J33" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="K33" s="15"/>
-    </row>
-    <row r="34" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A34" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="H34" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I34" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J34" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="K34" s="15"/>
-    </row>
-    <row r="35" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A35" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="H35" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I35" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J35" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="K35" s="15"/>
-    </row>
-    <row r="36" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A36" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I36" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="J36" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="K36" s="15"/>
-    </row>
-    <row r="37" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A37" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>35</v>
@@ -2446,91 +2694,98 @@
       <c r="D37" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>142</v>
+      <c r="E37" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>160</v>
+        <v>76</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>160</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="H37" s="3"/>
       <c r="I37" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-    </row>
-    <row r="38" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A38" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B38" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="15"/>
+    </row>
+    <row r="38" spans="1:14" ht="15.75">
+      <c r="A38" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="K38" s="15"/>
-    </row>
-    <row r="39" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A39" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="B39" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="F39" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="G39" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H39" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="I39" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-    </row>
-    <row r="40" spans="1:11" ht="19.5" customHeight="1">
+      <c r="C38" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="15"/>
+    </row>
+    <row r="39" spans="1:14" ht="15.75">
+      <c r="A39" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="15"/>
+    </row>
+    <row r="40" spans="1:14" ht="15.75">
       <c r="A40" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>35</v>
@@ -2542,7 +2797,7 @@
         <v>160</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>160</v>
@@ -2550,49 +2805,57 @@
       <c r="G40" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>160</v>
-      </c>
+      <c r="H40" s="3"/>
       <c r="I40" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-    </row>
-    <row r="41" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A41" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="J41" s="15"/>
-      <c r="K41" s="15"/>
-    </row>
-    <row r="42" spans="1:11" ht="19.5" customHeight="1">
+      <c r="J40" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="15"/>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="15"/>
+    </row>
+    <row r="42" spans="1:14" ht="15.75">
       <c r="A42" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>35</v>
@@ -2604,28 +2867,29 @@
         <v>160</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>160</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="H42" s="3"/>
       <c r="I42" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="K42" s="15"/>
-    </row>
-    <row r="43" spans="1:11" ht="19.5" customHeight="1">
+        <v>160</v>
+      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="15"/>
+    </row>
+    <row r="43" spans="1:14" ht="15.75">
       <c r="A43" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>35</v>
@@ -2637,155 +2901,218 @@
         <v>160</v>
       </c>
       <c r="E43" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="15"/>
+    </row>
+    <row r="44" spans="1:14" ht="15.75">
+      <c r="A44" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
-    </row>
-    <row r="44" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A44" s="5" t="s">
+      <c r="F44" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="15"/>
+    </row>
+    <row r="45" spans="1:14" ht="15.75">
+      <c r="A45" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H44" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="I44" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="J44" s="15"/>
-      <c r="K44" s="15"/>
-    </row>
-    <row r="45" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A45" s="5" t="s">
-        <v>178</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>160</v>
+        <v>213</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="E45" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H45" s="5"/>
+      <c r="I45" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="J45" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="15"/>
+    </row>
+    <row r="46" spans="1:14" ht="15.75">
+      <c r="A46" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="F46" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="G46" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="H46" s="5"/>
+      <c r="I46" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="I45" s="5" t="s">
+      <c r="J46" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-    </row>
-    <row r="46" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A46" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="B46" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="D46" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="E46" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="F46" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="G46" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="H46" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="I46" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-    </row>
-    <row r="47" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A47" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B47" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="D47" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="E47" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="F47" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="G47" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="H47" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="I47" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="K47" s="3"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="15"/>
+    </row>
+    <row r="47" spans="1:14" ht="15.75">
+      <c r="A47" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H47" s="5"/>
+      <c r="I47" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="J47" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="15"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:K47">
-    <sortCondition ref="E2:E47"/>
-    <sortCondition ref="D2:D47"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N48">
+    <sortCondition descending="1" ref="B2:B48"/>
+    <sortCondition ref="E2:E48"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A8E462E-16A7-434F-A9D4-A4A6CCC712A6}">
+  <dimension ref="B2:B8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="88.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" s="15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" s="15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="15" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" s="15" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="15" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="15" t="s">
+        <v>238</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/excel_files/mappings.xlsx
+++ b/excel_files/mappings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98BC229D-7433-4E48-BAE4-952CC2A1708E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05F08C4-3E0E-4A8B-99C4-DC3D7FD8DDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="16170" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28785" yWindow="15975" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
